--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_900_Crete_Greece.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_900_Crete_Greece.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb955c8a567144d12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rf1db4f4f52484fb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R5405f1cf16af46c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rfd4548795aed45e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R7f0bf335d1094f71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R59211ea73f74459e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R50da269a4ca04fd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0a4feba02ba946aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R08a0cc9c907c4fcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ra2429c4dcef24f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf3a30ffd3c67446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb7083ef9a18c4c14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ900CommercialTable" displayName="EEZ900CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ900CommercialTable" displayName="EEZ900CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ900FunctionalTable" displayName="EEZ900FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ900FunctionalTable" displayName="EEZ900FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ900ValidationTable" displayName="EEZ900ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ900ValidationTable" displayName="EEZ900ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5585,7 +5539,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38172d78598d44d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R130140363eac4a17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5595,20 +5549,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5616,552 +5560,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>29.559868827400003</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>29.559868827400003</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$74,A2,'Species'!$U$2:$U$74))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3808.048776500589</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>3808.048776500589</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>221.6921223433</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.008795280191037</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>102.04583417837925</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>221.6921223433</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>142.35055611392573</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$74,A3,'Species'!$U$2:$U$74))</x:f>
-        <x:v>31557.996901645216</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.008795280191037</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>102.04583417837925</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>22622.757555297358</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>8935.239346347858</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.3949668524938763</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.39496685249387636</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5.431119906999999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.9783441892256133</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>951.3584703157662</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>5.431119906999999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1591.7373435331237</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$74,A4,'Species'!$U$2:$U$74))</x:f>
-        <x:v>8644.916373178045</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.9783441892256133</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>951.3584703157662</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>5166.941926825026</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>3477.9744463530187</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.6731204831810755</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.6731204831810755</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>11.473886942600002</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3929174509045152</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>247.12543734423784</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>11.473886942600002</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>248.4853005569698</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$74,A5,'Species'!$U$2:$U$74))</x:f>
-        <x:v>2851.0922454886527</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3929174509045152</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>247.12543734423784</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2835.4893287283653</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>15.602916760287371</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0055027245569939</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.005502724556993775</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>846.382366694</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.691229750221147</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>491.1676446647884</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>846.382366694</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>678.8721033164344</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$74,A6,'Species'!$U$2:$U$74))</x:f>
-        <x:v>574585.3774874974</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.691229750221147</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>491.1676446647884</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>415715.6335349012</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>158869.7439525962</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3821596570754378</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.3821596570754378</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2010.1983644457</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3733994451956897</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>236.26502972358603</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2010.1983644457</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>546.6107252426751</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$74,A7,'Species'!$U$2:$U$74))</x:f>
-        <x:v>1098795.9858713034</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3733994451956897</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>236.26502972358603</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>474939.5763260673</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>623856.409545236</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>2.3135490084257175</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>1.3135490084257173</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>32.8381816542</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7573128979390757</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>571.8905206035612</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>32.8381816542</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>591.8174913842341</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$74,A8,'Species'!$U$2:$U$74))</x:f>
-        <x:v>19434.210288208422</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7573128979390757</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>571.8905206035612</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>18779.84480189475</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>654.3654863136726</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0348440305666238</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.03484403056662384</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>31.535768166000004</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.839849569029617</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>691.5913759290423</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>31.535768166000004</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>774.9902915489661</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$74,A9,'Species'!$U$2:$U$74))</x:f>
-        <x:v>24439.914165188948</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.839849569029617</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>691.5913759290423</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>21809.865296903234</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2630.048868285714</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1205898721739997</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.12058987217399975</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>430.00842267859997</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.414508509279381</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2597.2186290907557</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>430.00842267859997</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2703.400011097016</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$74,A10,'Species'!$U$2:$U$74))</x:f>
-        <x:v>1162484.7746411376</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.414508509279381</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2597.2186290907557</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1116825.8860467917</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>45658.88859434589</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0408827277060742</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.04088272770607407</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re211fffd7b554d81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08c9975da94a4e95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6171,20 +5756,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6192,1254 +5767,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>234.3780224574</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.988672274911034</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>974.2541735360952</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>234.3780224574</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1121.7051059743817</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$74,A2,'Species'!$U$2:$U$74))</x:f>
-        <x:v>262903.02451864386</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.988672274911034</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>974.2541735360952</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>228343.7665642586</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>34559.25795438525</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1513474988802022</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.15134749888020205</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>4.7729817957</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.14</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1380.3842646028838</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>4.7729817957</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$74,A3,'Species'!$U$2:$U$74))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>6588.548966020297</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.14</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>6588.548966020297</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>22.662495476000004</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.53</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>3388.4415613920273</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>22.662495476000004</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>3388.4415613920273</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$74,A4,'Species'!$U$2:$U$74))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>76790.5415557372</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.53</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>3388.4415613920273</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>76790.5415557372</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>28.134614485900002</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8522054633825213</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>711.5500661820506</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>28.134614485900002</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>787.0789963686055</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$74,A5,'Species'!$U$2:$U$74))</x:f>
-        <x:v>22144.164132779806</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8522054633825213</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>711.5500661820506</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>20019.186799448627</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>2124.9773333311787</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1061470355723793</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.10614703557237926</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3.6515848201</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3.6515848201</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$74,A6,'Species'!$U$2:$U$74))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>8365.297545704925</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>8365.297545704925</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>336.79581472940004</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.4467595010049905</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2797.4317585155345</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>336.79581472940004</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2852.791514473919</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$74,A7,'Species'!$U$2:$U$74))</x:f>
-        <x:v>960808.2423703626</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.4467595010049905</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2797.4317585155345</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>942163.3082591377</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>18644.934111224953</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.019789492912514</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.019789492912514004</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4.0674840036</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.84</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>691.8309709189363</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4.0674840036</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$74,A8,'Species'!$U$2:$U$74))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>2814.0114074078297</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.84</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>2814.0114074078297</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>169.59457966349999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.463921077643516</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2910.1882147721603</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>169.59457966349999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2995.02439365826</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$74,A9,'Species'!$U$2:$U$74))</x:f>
-        <x:v>507939.9031244015</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.463921077643516</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2910.1882147721603</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>493552.14702595596</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>14387.756098445563</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0291514406028688</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.02915144060286888</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>25.550404517300002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.84281683327355</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>696.3327689691548</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>25.550404517300002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>799.0402850981404</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$74,A10,'Species'!$U$2:$U$74))</x:f>
-        <x:v>20415.80250987621</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.84281683327355</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>696.3327689691548</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>17791.583925813513</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2624.2185840626953</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1474977492169913</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.14749774921699133</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>99.65232082089999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3869632384997845</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>243.76044749914834</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>99.65232082089999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>255.30281322425643</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$74,A11,'Species'!$U$2:$U$74))</x:f>
-        <x:v>25441.51784990191</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3869632384997845</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>243.76044749914834</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>24291.29431763128</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1150.2235322706292</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0473512657345625</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0473512657345626</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>11.7851102748</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.109837414375995</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1287.767363534901</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>11.7851102748</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1918.3079639197404</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$74,A12,'Species'!$U$2:$U$74))</x:f>
-        <x:v>22607.4708958212</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.109837414375995</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1287.767363534901</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>15176.480387547268</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>7430.9905082739315</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.4896385933046288</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.4896385933046288</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>233.9879485493</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.5275351959327876</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>336.9265197095018</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>233.9879485493</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>465.60658630692154</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$74,A13,'Species'!$U$2:$U$74))</x:f>
-        <x:v>108946.32996099917</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.5275351959327876</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>336.9265197095018</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>78836.74515868162</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>30109.58480231755</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.3819232356905826</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.3819232356905825</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1426.5117931798002</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.3184984073180264</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>208.20847696062668</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1426.5117931798002</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>287.2737980848555</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$74,A14,'Species'!$U$2:$U$74))</x:f>
-        <x:v>409799.4608395991</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.3184984073180264</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>208.20847696062668</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>297011.8478243387</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>112787.61301526037</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.3797411242731508</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.3797411242731508</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>205.11743570080003</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.075262025494821</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>1189.2195099743903</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>205.11743570080003</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1557.3556509357336</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$74,A15,'Species'!$U$2:$U$74))</x:f>
-        <x:v>319440.7975940879</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.075262025494821</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>1189.2195099743903</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>243929.65637130893</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>75511.14122277897</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.309561134738927</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.30956113473892716</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>83.4303578733</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.752208783748355</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>56.520862923192695</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>83.4303578733</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>145.48861700762063</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$74,A16,'Species'!$U$2:$U$74))</x:f>
-        <x:v>12138.16738343727</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.752208783748355</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>56.520862923192695</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4715.5558209897</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>7422.611562447571</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>2.574069281378948</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>1.5740692813789476</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>122.0398015224</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.7000000000000006</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>50.1187233627273</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>122.0398015224</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$74,A17,'Species'!$U$2:$U$74))</x:f>
-        <x:v>6116.479051743306</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.7000000000000006</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>50.1187233627273</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>6116.479051743312</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>-6.366462912410498e-12</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>-1.0408705496336059e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>111.31133143230001</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.559209547703654</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>362.4178233505982</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>111.31133143230001</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>375.4157096628427</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$74,A18,'Species'!$U$2:$U$74))</x:f>
-        <x:v>41788.0224831728</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.559209547703654</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>362.4178233505982</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>40341.21045195119</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>1446.8120312216051</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0358643683472226</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.03586436834722263</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>379.1817222862</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.0895273226101843</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>122.89304994023448</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>379.1817222862</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>174.36799733622803</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$74,A19,'Species'!$U$2:$U$74))</x:f>
-        <x:v>66117.15754154648</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.0895273226101843</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>122.89304994023448</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>46598.7983333421</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>19518.359208204376</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.4188597111148833</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.4188597111148833</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>41.03375577</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.189109571738016</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>154.5644353715457</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>41.03375577</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>162.28446304829293</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$74,A20,'Species'!$U$2:$U$74))</x:f>
-        <x:v>6659.141021989241</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.189109571738016</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>154.5644353715457</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>6342.359291763955</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>316.7817302252861</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.049946985916842</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.04994698591684197</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>71.7631275681</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.703532305658758</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>505.28022958432814</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>71.7631275681</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>519.6055158849136</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$74,A21,'Species'!$U$2:$U$74))</x:f>
-        <x:v>37288.51692153747</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.703532305658758</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>505.28022958432814</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>36260.489573299</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>1028.0273482384728</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0283511712151696</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.028351171215169623</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>1.7795350869</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.1951910075963115</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>156.74402963988254</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>1.7795350869</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>157.13026932232265</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$74,A22,'Species'!$U$2:$U$74))</x:f>
-        <x:v>279.61882747311984</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.1951910075963115</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>156.74402963988254</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>278.93150040626455</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0.6873270668552891</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.002464142866095</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.0024641428660950636</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>1.9178796451</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>1.9178796451</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$74,A23,'Species'!$U$2:$U$74))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>1210.100247904911</x:v>
       </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>1210.100247904911</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R082fff0c98af4e37"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R913b5c62146a4677"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7614,7 +6375,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7713,7 +6474,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>2926602.3167501483</x:v>
+        <x:v>2082504.0435939096</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7727,7 +6488,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>2926602.3167501483</x:v>
+        <x:v>2597538.3403803934</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7741,7 +6502,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-844098.2731562387</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7755,7 +6516,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-329063.9763697549</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7766,9 +6527,9 @@
         <x:v>EEZ_900</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7780,47 +6541,19 @@
         <x:v>EEZ_900</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_900</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_900</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0cf190779f44a7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e83cb4054cc4178"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7867,7 +6600,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
